--- a/Result/profitability/6103.xlsx
+++ b/Result/profitability/6103.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.93</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1125</v>
+        <v>0.10375</v>
       </c>
       <c r="N2" t="n">
-        <v>11.6575</v>
+        <v>10.3675</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.16</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.01875000000000002</v>
+        <v>-0.3775</v>
       </c>
       <c r="N3" t="n">
-        <v>10.09</v>
+        <v>9.026250000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-1.67</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.56375</v>
+        <v>-0.585</v>
       </c>
       <c r="N4" t="n">
-        <v>3.728750000000001</v>
+        <v>4.057499999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.15</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.70625</v>
+        <v>-0.5625</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.009999999999999343</v>
+        <v>-0.3037499999999995</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.75</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.63375</v>
+        <v>-0.7062499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-9.401249999999999</v>
+        <v>-10.79</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.44</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.73875</v>
+        <v>-0.80875</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.39125</v>
+        <v>-12.97875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-1.29</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9475</v>
+        <v>-0.94625</v>
       </c>
       <c r="N8" t="n">
-        <v>-11.145</v>
+        <v>-11.80375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>-0.83</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.715</v>
+        <v>-0.7150000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>10.29125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6103</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>17</v>
+      </c>
+      <c r="D75" t="n">
+        <v>16</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-16.41%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.20625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.18375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.05263157894736847</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.4582608695652174</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.8646616541353384</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2738927738927739</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
